--- a/02_Codigo/03_HybridTugboat/01_codes/02_Pnom025/Comparation_025.xlsx
+++ b/02_Codigo/03_HybridTugboat/01_codes/02_Pnom025/Comparation_025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell PC\Desktop\Tesis Magister\02_Codigo\03_HybridTugboat\01_codes\02_Pnom025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desar\Documents\Tesis Magister\Tesis_Msc_LSZ\02_Codigo\03_HybridTugboat\01_codes\02_Pnom025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B55B557-ACD1-4FAE-9104-970F997020C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D6C6CD-525D-4740-9BF9-661E4A08B572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{CC8E70EA-9981-4FE1-9A98-EC6DB5F1210E}"/>
+    <workbookView xWindow="-28920" yWindow="-11610" windowWidth="29040" windowHeight="15840" xr2:uid="{CC8E70EA-9981-4FE1-9A98-EC6DB5F1210E}"/>
   </bookViews>
   <sheets>
     <sheet name="1_Maneuver" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="16">
   <si>
     <t>Pot_acc [kW]</t>
   </si>
@@ -76,6 +76,15 @@
   </si>
   <si>
     <t>Hyb Improvement</t>
+  </si>
+  <si>
+    <t>Batt</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Total Consumption</t>
   </si>
 </sst>
 </file>
@@ -130,7 +139,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -139,6 +148,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -474,16 +485,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F86E1CB-682A-45B9-8296-40FE06F59BBE}">
-  <dimension ref="B2:L16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:L25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B2" s="5" t="s">
         <v>6</v>
       </c>
@@ -495,7 +506,7 @@
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -515,7 +526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>3</v>
       </c>
@@ -534,8 +545,15 @@
       <c r="H4" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="1">
+        <f>SUM(G4:G6)</f>
+        <v>1928.535921921922</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>4</v>
       </c>
@@ -555,7 +573,7 @@
         <v>2.7235268068349998</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>5</v>
       </c>
@@ -575,213 +593,301 @@
         <v>2.4253314322500001</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C7" s="1">
         <v>5365.5438438438441</v>
       </c>
       <c r="D7" s="1">
         <v>14.325076506750001</v>
       </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
       <c r="G7" s="1">
-        <v>1928.535921921922</v>
+        <f>C7-SUM(G4:G6)</f>
+        <v>3437.0079219219224</v>
       </c>
       <c r="H7" s="1">
-        <v>5.1488582390849995</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
+        <f>D7-SUM(H4:H6)</f>
+        <v>9.1762182676650017</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="F8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="7">
+        <f>SUM(G4:G7)</f>
+        <v>5365.5438438438441</v>
+      </c>
+      <c r="H8" s="7">
+        <f>SUM(H4:H7)</f>
+        <v>14.325076506750001</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="F9" s="5" t="s">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="F10" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="J9" s="5" t="s">
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="J10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" t="s">
         <v>9</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>10</v>
       </c>
-      <c r="F10" t="s">
-        <v>0</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="F11" t="s">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
         <v>9</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H11" t="s">
         <v>10</v>
       </c>
-      <c r="J10" t="s">
-        <v>0</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="J11" t="s">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
         <v>9</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C12" s="2">
         <f>C4/$C$7</f>
         <v>0.39079576886462902</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D12" s="2">
         <f>D4/$D$7</f>
         <v>0.39079576886462902</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F12" t="s">
         <v>3</v>
       </c>
-      <c r="G11" s="2">
-        <f>G4/$G$7</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <f>H4/$H$7</f>
-        <v>0</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="G12" s="2">
+        <f>G4/$G$8</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <f>H4/$H$8</f>
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
         <v>3</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K12" s="2">
         <f>G4/$C$7</f>
         <v>0</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L12" s="2">
         <f>H4/$D$7</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="2">
-        <f t="shared" ref="C12:C13" si="0">C5/$C$7</f>
+      <c r="C13" s="2">
+        <f>C5/$C$7</f>
         <v>0.43989753102056328</v>
       </c>
-      <c r="D12" s="2">
-        <f t="shared" ref="D12:D13" si="1">D5/$D$7</f>
+      <c r="D13" s="2">
+        <f>D5/$D$7</f>
         <v>0.43989753102056317</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F13" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="2">
-        <f t="shared" ref="G12:G13" si="2">G5/$G$7</f>
-        <v>0.52895742713611704</v>
-      </c>
-      <c r="H12" s="2">
-        <f t="shared" ref="H12:H13" si="3">H5/$H$7</f>
-        <v>0.52895742713611704</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="G13" s="2">
+        <f t="shared" ref="G13:G14" si="0">G5/$G$8</f>
+        <v>0.1901230199749139</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" ref="H13:H15" si="1">H5/$H$8</f>
+        <v>0.19012301997491388</v>
+      </c>
+      <c r="J13" t="s">
         <v>4</v>
       </c>
-      <c r="K12" s="2">
-        <f t="shared" ref="K12:K13" si="4">G5/$C$7</f>
+      <c r="K13" s="2">
+        <f>G5/$C$7</f>
         <v>0.1901230199749139</v>
       </c>
-      <c r="L12" s="2">
-        <f t="shared" ref="L12:L13" si="5">H5/$D$7</f>
+      <c r="L13" s="2">
+        <f>H5/$D$7</f>
         <v>0.19012301997491388</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C14" s="2">
+        <f>C6/$C$7</f>
+        <v>0.16930670011480775</v>
+      </c>
+      <c r="D14" s="2">
+        <f>D6/$D$7</f>
+        <v>0.16930670011480775</v>
+      </c>
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="2">
         <f t="shared" si="0"/>
         <v>0.16930670011480775</v>
       </c>
-      <c r="D13" s="2">
+      <c r="H14" s="2">
         <f t="shared" si="1"/>
         <v>0.16930670011480775</v>
       </c>
-      <c r="F13" t="s">
+      <c r="J14" t="s">
         <v>8</v>
       </c>
-      <c r="G13" s="2">
+      <c r="K14" s="2">
+        <f>G6/$C$7</f>
+        <v>0.16930670011480775</v>
+      </c>
+      <c r="L14" s="2">
+        <f>H6/$D$7</f>
+        <v>0.16930670011480775</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C15" s="2">
+        <f>SUM(C12:C14)</f>
+        <v>1</v>
+      </c>
+      <c r="D15" s="2">
+        <f>SUM(D12:D14)</f>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2">
+        <f>G7/G8</f>
+        <v>0.64057027991027837</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="1"/>
+        <v>0.64057027991027837</v>
+      </c>
+      <c r="K15" s="2">
+        <f>SUM(K12:K14)</f>
+        <v>0.35942972008972163</v>
+      </c>
+      <c r="L15" s="2">
+        <f>SUM(L12:L14)</f>
+        <v>0.35942972008972163</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="G16" s="6">
+        <f>SUM(G12:G15)</f>
+        <v>1</v>
+      </c>
+      <c r="H16" s="6">
+        <f>SUM(H12:H15)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="6:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K17" s="4">
+        <f>1-G7/C7</f>
+        <v>0.35942972008972163</v>
+      </c>
+    </row>
+    <row r="19" spans="6:11" x14ac:dyDescent="0.35">
+      <c r="F19" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="6:11" x14ac:dyDescent="0.35">
+      <c r="F20" t="s">
+        <v>0</v>
+      </c>
+      <c r="G20" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="6:11" x14ac:dyDescent="0.35">
+      <c r="F21" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="2">
+        <f>G4/$K$4</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="6:11" x14ac:dyDescent="0.35">
+      <c r="F22" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="2">
+        <f t="shared" ref="G22:G23" si="2">G5/$K$4</f>
+        <v>0.52895742713611704</v>
+      </c>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="6:11" x14ac:dyDescent="0.35">
+      <c r="F23" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="2">
         <f t="shared" si="2"/>
         <v>0.4710425728638829</v>
       </c>
-      <c r="H13" s="2">
-        <f t="shared" si="3"/>
-        <v>0.47104257286388301</v>
-      </c>
-      <c r="J13" t="s">
-        <v>8</v>
-      </c>
-      <c r="K13" s="2">
-        <f t="shared" si="4"/>
-        <v>0.16930670011480775</v>
-      </c>
-      <c r="L13" s="2">
-        <f t="shared" si="5"/>
-        <v>0.16930670011480775</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C14" s="2">
-        <f>SUM(C11:C13)</f>
-        <v>1</v>
-      </c>
-      <c r="D14" s="2">
-        <f>SUM(D11:D13)</f>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="G14" s="2">
-        <f>SUM(G11:G13)</f>
-        <v>1</v>
-      </c>
-      <c r="H14" s="2">
-        <f>SUM(H11:H13)</f>
-        <v>1</v>
-      </c>
-      <c r="K14" s="2">
-        <f>SUM(K11:K13)</f>
-        <v>0.35942972008972163</v>
-      </c>
-      <c r="L14" s="2">
-        <f>SUM(L11:L13)</f>
-        <v>0.35942972008972163</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="J16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K16" s="4">
-        <f>1-G7/C7</f>
-        <v>0.64057027991027837</v>
-      </c>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="6:11" x14ac:dyDescent="0.35">
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="6:11" x14ac:dyDescent="0.35">
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="F19:H19"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="J10:L10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -789,16 +895,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B17609A2-A501-41D4-9B3C-7FBDBE908257}">
-  <dimension ref="B2:L16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:L24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B2" s="5" t="s">
         <v>6</v>
       </c>
@@ -810,7 +916,7 @@
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -830,7 +936,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>3</v>
       </c>
@@ -849,8 +955,15 @@
       <c r="H4" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="1">
+        <f>SUM(G4:G6)</f>
+        <v>4029.9572177177174</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>4</v>
       </c>
@@ -870,7 +983,7 @@
         <v>2.2010703599362498</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>5</v>
       </c>
@@ -890,213 +1003,298 @@
         <v>8.5582202437500001</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C7" s="1">
         <v>6384.5624624624634</v>
       </c>
       <c r="D7" s="1">
         <v>17.045680437750001</v>
       </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
       <c r="G7" s="1">
-        <v>4029.9572177177174</v>
+        <f>C7-SUM(G4:G6)</f>
+        <v>2354.605244744746</v>
       </c>
       <c r="H7" s="1">
-        <v>10.759290603686249</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
+        <f>D7-SUM(H4:H6)</f>
+        <v>6.2863898340637512</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="G8" s="1">
+        <f>SUM(G4:G7)</f>
+        <v>6384.5624624624634</v>
+      </c>
+      <c r="H8" s="1">
+        <f>SUM(H4:H7)</f>
+        <v>17.045680437750001</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="F9" s="5" t="s">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="F10" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="J9" s="5" t="s">
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="J10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" t="s">
         <v>9</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>10</v>
       </c>
-      <c r="F10" t="s">
-        <v>0</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="F11" t="s">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
         <v>9</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H11" t="s">
         <v>10</v>
       </c>
-      <c r="J10" t="s">
-        <v>0</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="J11" t="s">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
         <v>9</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C12" s="2">
         <f>C4/$C$7</f>
         <v>0.1941965588636215</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D12" s="2">
         <f>D4/$D$7</f>
         <v>0.19419655886362153</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F12" t="s">
         <v>3</v>
       </c>
-      <c r="G11" s="2">
-        <f>G4/$G$7</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <f>H4/$H$7</f>
-        <v>0</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="G12" s="2">
+        <f>G4/$G$8</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <f>H4/$H$8</f>
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
         <v>3</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K12" s="2">
         <f>G4/$C$7</f>
         <v>0</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L12" s="2">
         <f>H4/$D$7</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="2">
-        <f t="shared" ref="C12:C13" si="0">C5/$C$7</f>
+      <c r="C13" s="2">
+        <f>C5/$C$7</f>
         <v>0.30372784051696017</v>
       </c>
-      <c r="D12" s="2">
-        <f t="shared" ref="D12:D13" si="1">D5/$D$7</f>
+      <c r="D13" s="2">
+        <f>D5/$D$7</f>
         <v>0.30372784051696017</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F13" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="2">
-        <f t="shared" ref="G12:G13" si="2">G5/$G$7</f>
-        <v>0.2045739297330755</v>
-      </c>
-      <c r="H12" s="2">
-        <f t="shared" ref="H12:H13" si="3">H5/$H$7</f>
-        <v>0.20457392973307545</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="G13" s="2">
+        <f t="shared" ref="G13:G14" si="0">G5/$G$8</f>
+        <v>0.12912774987038225</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" ref="H13:H15" si="1">H5/$H$8</f>
+        <v>0.12912774987038225</v>
+      </c>
+      <c r="J13" t="s">
         <v>4</v>
       </c>
-      <c r="K12" s="2">
-        <f t="shared" ref="K12" si="4">G5/$C$7</f>
+      <c r="K13" s="2">
+        <f>G5/$C$7</f>
         <v>0.12912774987038225</v>
       </c>
-      <c r="L12" s="2">
-        <f t="shared" ref="L12:L13" si="5">H5/$D$7</f>
+      <c r="L13" s="2">
+        <f>H5/$D$7</f>
         <v>0.12912774987038225</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="2">
-        <f t="shared" si="0"/>
+      <c r="C14" s="2">
+        <f>C6/$C$7</f>
         <v>0.50207560061941825</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D14" s="2">
+        <f>D6/$D$7</f>
+        <v>0.50207560061941825</v>
+      </c>
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="2">
+        <f>G6/$G$8</f>
+        <v>0.50207560061941814</v>
+      </c>
+      <c r="H14" s="2">
         <f t="shared" si="1"/>
         <v>0.50207560061941825</v>
       </c>
-      <c r="F13" t="s">
+      <c r="J14" t="s">
         <v>8</v>
       </c>
-      <c r="G13" s="2">
+      <c r="K14" s="2">
+        <f>G6/$C$7</f>
+        <v>0.50207560061941814</v>
+      </c>
+      <c r="L14" s="2">
+        <f>H6/$D$7</f>
+        <v>0.50207560061941825</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C15" s="2">
+        <f>SUM(C12:C14)</f>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="D15" s="2">
+        <f>SUM(D12:D14)</f>
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2">
+        <f>G7/$G$8</f>
+        <v>0.36879664951019958</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="1"/>
+        <v>0.36879664951019953</v>
+      </c>
+      <c r="K15" s="2">
+        <f>SUM(K12:K14)</f>
+        <v>0.63120335048980036</v>
+      </c>
+      <c r="L15" s="2">
+        <f>SUM(L12:L14)</f>
+        <v>0.63120335048980047</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="G16" s="6">
+        <f>SUM(G12:G15)</f>
+        <v>1</v>
+      </c>
+      <c r="H16" s="6">
+        <f>SUM(H12:H15)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="6:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K17" s="4">
+        <f>1-G7/C7</f>
+        <v>0.63120335048980047</v>
+      </c>
+    </row>
+    <row r="18" spans="6:11" x14ac:dyDescent="0.35">
+      <c r="F18" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="6:11" x14ac:dyDescent="0.35">
+      <c r="F19" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="6:11" x14ac:dyDescent="0.35">
+      <c r="F20" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="2">
+        <f>G4/$K$4</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="6:11" x14ac:dyDescent="0.35">
+      <c r="F21" t="s">
+        <v>4</v>
+      </c>
+      <c r="G21" s="2">
+        <f t="shared" ref="G21:G23" si="2">G5/$K$4</f>
+        <v>0.2045739297330755</v>
+      </c>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="6:11" x14ac:dyDescent="0.35">
+      <c r="F22" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2">
         <f t="shared" si="2"/>
         <v>0.79542607026692447</v>
       </c>
-      <c r="H13" s="2">
-        <f t="shared" si="3"/>
-        <v>0.79542607026692458</v>
-      </c>
-      <c r="J13" t="s">
-        <v>8</v>
-      </c>
-      <c r="K13" s="2">
-        <f>G6/$C$7</f>
-        <v>0.50207560061941814</v>
-      </c>
-      <c r="L13" s="2">
-        <f t="shared" si="5"/>
-        <v>0.50207560061941825</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C14" s="2">
-        <f>SUM(C11:C13)</f>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="D14" s="2">
-        <f>SUM(D11:D13)</f>
-        <v>1</v>
-      </c>
-      <c r="G14" s="2">
-        <f>SUM(G11:G13)</f>
-        <v>1</v>
-      </c>
-      <c r="H14" s="2">
-        <f>SUM(H11:H13)</f>
-        <v>1</v>
-      </c>
-      <c r="K14" s="2">
-        <f>SUM(K11:K13)</f>
-        <v>0.63120335048980036</v>
-      </c>
-      <c r="L14" s="2">
-        <f>SUM(L11:L13)</f>
-        <v>0.63120335048980047</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="J16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K16" s="4">
-        <f>1-G7/C7</f>
-        <v>0.36879664951019964</v>
-      </c>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="6:11" x14ac:dyDescent="0.35">
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="6:11" x14ac:dyDescent="0.35">
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="F18:H18"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="J10:L10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
